--- a/TestFiles/ExcelFiles/MedicareComPayment.xlsx
+++ b/TestFiles/ExcelFiles/MedicareComPayment.xlsx
@@ -74,7 +74,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>8.22</v>
+        <v>8.06</v>
       </c>
     </row>
   </sheetData>

--- a/TestFiles/ExcelFiles/MedicareComPayment.xlsx
+++ b/TestFiles/ExcelFiles/MedicareComPayment.xlsx
@@ -74,7 +74,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>3.56</v>
+        <v>4.64</v>
       </c>
     </row>
   </sheetData>
